--- a/data/trans_bre/IP04D$aparatos-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Edad-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 16,39</t>
+          <t>-2,37; 16,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 11,44</t>
+          <t>-7,46; 12,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 11,77</t>
+          <t>-15,75; 11,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 33,27</t>
+          <t>-3,81; 35,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 23,25</t>
+          <t>-12,84; 23,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 22,44</t>
+          <t>-23,11; 20,07</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 8,48</t>
+          <t>-6,09; 7,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 2,84</t>
+          <t>-12,84; 2,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 4,08</t>
+          <t>-13,6; 4,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 13,72</t>
+          <t>-8,99; 12,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 5,2</t>
+          <t>-22,79; 4,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 6,45</t>
+          <t>-19,6; 7,56</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 13,39</t>
+          <t>-3,86; 14,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 11,32</t>
+          <t>-5,57; 11,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,44; 22,84</t>
+          <t>5,15; 23,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 24,62</t>
+          <t>-5,71; 27,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 24,73</t>
+          <t>-10,52; 24,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,72; 48,79</t>
+          <t>8,97; 49,26</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 7,92</t>
+          <t>-8,75; 8,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 6,31</t>
+          <t>-11,12; 6,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 17,37</t>
+          <t>-6,02; 17,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 13,17</t>
+          <t>-12,94; 13,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 13,03</t>
+          <t>-19,64; 13,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 33,45</t>
+          <t>-9,86; 34,69</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,85</t>
+          <t>-1,7; 6,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 3,28</t>
+          <t>-5,33; 3,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 10,58</t>
+          <t>-0,98; 10,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 11,36</t>
+          <t>-2,67; 11,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 6,34</t>
+          <t>-9,54; 6,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 19,01</t>
+          <t>-1,53; 17,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$aparatos-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Edad-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 16,81</t>
+          <t>-2,07; 17,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 12,0</t>
+          <t>-7,03; 12,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 11,12</t>
+          <t>-15,61; 10,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 35,21</t>
+          <t>-3,36; 36,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 23,94</t>
+          <t>-12,15; 24,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 20,07</t>
+          <t>-23,3; 19,36</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 7,63</t>
+          <t>-6,36; 7,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 2,41</t>
+          <t>-13,04; 2,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 4,36</t>
+          <t>-15,29; 2,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 12,62</t>
+          <t>-9,05; 12,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 4,91</t>
+          <t>-22,94; 4,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 7,56</t>
+          <t>-21,68; 4,62</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 14,77</t>
+          <t>-4,15; 13,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 11,15</t>
+          <t>-5,3; 11,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 23,11</t>
+          <t>4,27; 22,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 27,82</t>
+          <t>-6,67; 24,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 24,54</t>
+          <t>-9,41; 24,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,97; 49,26</t>
+          <t>7,64; 49,39</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 8,35</t>
+          <t>-8,34; 8,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 6,78</t>
+          <t>-10,23; 6,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 17,77</t>
+          <t>-6,09; 17,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 13,77</t>
+          <t>-12,53; 13,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,64; 13,73</t>
+          <t>-18,23; 13,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 34,69</t>
+          <t>-9,83; 34,44</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,83</t>
+          <t>-1,89; 6,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 3,13</t>
+          <t>-5,19; 3,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,02</t>
+          <t>-1,82; 10,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 11,48</t>
+          <t>-2,95; 10,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 6,3</t>
+          <t>-9,56; 6,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 17,69</t>
+          <t>-3,23; 18,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$aparatos-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Edad-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,54</t>
+          <t>-3,51</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,56%</t>
+          <t>-5,69%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 17,02</t>
+          <t>-2,4; 16,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 12,4</t>
+          <t>-8,17; 11,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 10,73</t>
+          <t>-16,33; 10,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 36,38</t>
+          <t>-4,21; 33,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 24,55</t>
+          <t>-13,2; 23,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 19,36</t>
+          <t>-23,76; 20,47</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-5,24</t>
+          <t>-4,59</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-7,94%</t>
+          <t>-6,92%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 7,85</t>
+          <t>-5,94; 8,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 2,16</t>
+          <t>-12,1; 2,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 2,9</t>
+          <t>-13,35; 3,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 12,68</t>
+          <t>-8,64; 13,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 4,18</t>
+          <t>-21,82; 5,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 4,62</t>
+          <t>-18,91; 6,22</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,81</t>
+          <t>11,47</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 13,33</t>
+          <t>-3,98; 13,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 11,27</t>
+          <t>-5,76; 11,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 22,97</t>
+          <t>2,62; 20,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 24,05</t>
+          <t>-6,27; 24,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 24,29</t>
+          <t>-10,28; 24,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 49,39</t>
+          <t>5,15; 41,4</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,83</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 8,57</t>
+          <t>-8,78; 7,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 6,5</t>
+          <t>-11,87; 6,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 17,86</t>
+          <t>-7,24; 9,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 13,73</t>
+          <t>-12,91; 13,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 13,54</t>
+          <t>-20,27; 13,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 34,44</t>
+          <t>-11,3; 17,2</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 6,38</t>
+          <t>-1,47; 6,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 3,16</t>
+          <t>-5,23; 3,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 10,24</t>
+          <t>-2,29; 7,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 10,56</t>
+          <t>-2,35; 11,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 6,12</t>
+          <t>-9,61; 6,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 18,16</t>
+          <t>-3,68; 12,79</t>
         </is>
       </c>
     </row>
